--- a/testes/perfis_exemplo/perfil_minimo/matriz_curricular.xlsx
+++ b/testes/perfis_exemplo/perfil_minimo/matriz_curricular.xlsx
@@ -7,14 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Curso" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Componentes" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pre-requisitos" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Correquisitos" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equivalencias" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Areas" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Temas" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competencias" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Componentes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equivalencias" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nucleos" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Areas" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Temas" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conteudos" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -420,30 +418,356 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:U5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>campo</t>
+          <t>codigo</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>valor</t>
+          <t>nome</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>tipo</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>periodo</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ativo</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>obrigatorio</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>codigo_provisorio</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>cht</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>chp</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>chd</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>che</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>tot</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>nucleo_id</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>unidade_oferta</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>observacoes</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>pre_requisitos</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>correquisitos</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>areas</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>temas</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>conteudos</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>competencias</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>versao_curricular</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>teste-1</t>
+          <t>Fundamentos de Teste</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>disciplina</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>30</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>BASICO</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>UA1</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>MATEMATICA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Teste Avançado</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>disciplina</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>30</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>30</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>TECNOLOGICO</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>UA1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>COMPUTACAO</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EXT1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Extensão de Teste</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>extensao</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>15</v>
+      </c>
+      <c r="L4" t="n">
+        <v>15</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>HUMANISTICO</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>UA1</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>EXTENSAO</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>OPT1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Optativa de Teste</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>carga_optativa</t>
+        </is>
+      </c>
+      <c r="E5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>30</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>30</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>OPTATIVO</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>UA1</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>COMPUTACAO</t>
         </is>
       </c>
     </row>
@@ -458,311 +782,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>codigo</t>
+          <t>codigo_origem</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>nome</t>
+          <t>codigo_destino</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>tipo</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>periodo</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>ativo</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>obrigatorio</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>codigo_provisorio</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>cht</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>chp</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>chd</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>che</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>tot</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>nucleo_id</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>unidade_oferta</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>ementa</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>observacoes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Fundamentos de Teste</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>disciplina</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>30</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>BASICO</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>UA1</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>D2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Teste Avançado</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>disciplina</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G3" t="b">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>30</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>30</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>TECNOLOGICO</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>UA1</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>EXT1</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Extensão de Teste</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>extensao</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>15</v>
-      </c>
-      <c r="L4" t="n">
-        <v>15</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>HUMANISTICO</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>UA1</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>OPT1</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Optativa de Teste</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>carga_optativa</t>
-        </is>
-      </c>
-      <c r="E5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>30</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>30</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>OPTATIVO</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>UA1</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
+          <t>observacao</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -775,44 +813,72 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>codigo_componente</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>codigo_prerequisito</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>opcional</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>carga_horaria_minima</t>
+          <t>descricao</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>BASICO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="C2" t="b">
-        <v>0</v>
+          <t>Núcleo Básico de Teste</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>TECNOLOGICO</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Núcleo Tecnológico de Teste</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>HUMANISTICO</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Núcleo Humanístico de Teste</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>OPTATIVO</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Núcleo Optativo de Teste</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -826,23 +892,59 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>codigo_componente</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>codigo_correquisito</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>opcional</t>
+          <t>descricao</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MATEMATICA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>COMPUTACAO</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Computação</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EXTENSAO</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Extensão</t>
         </is>
       </c>
     </row>
@@ -857,23 +959,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>codigo_origem</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>codigo_destino</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>observacao</t>
+          <t>descricao</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>fonte_normativa</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
         </is>
       </c>
     </row>
@@ -888,130 +1000,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>codigo_componente</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>area_id</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>MATEMATICA</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>D2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>COMPUTACAO</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>EXT1</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>EXTENSAO</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>OPT1</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>COMPUTACAO</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>codigo_componente</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>tema_id</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>codigo_componente</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>competencia_id</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>D2</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>C1</t>
+          <t>descricao</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>obrigatorio</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>fonte</t>
         </is>
       </c>
     </row>

--- a/testes/perfis_exemplo/perfil_minimo/matriz_curricular.xlsx
+++ b/testes/perfis_exemplo/perfil_minimo/matriz_curricular.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,75 +454,65 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>codigo_provisorio</t>
+          <t>cht</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>cht</t>
+          <t>chp</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>chp</t>
+          <t>chd</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>chd</t>
+          <t>che</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>che</t>
+          <t>tot</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>tot</t>
+          <t>nucleo_id</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>nucleo_id</t>
+          <t>observacoes</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>unidade_oferta</t>
+          <t>pre_requisitos</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>observacoes</t>
+          <t>correquisitos</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>pre_requisitos</t>
+          <t>areas</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>correquisitos</t>
+          <t>temas</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>areas</t>
+          <t>conteudos</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
-        <is>
-          <t>temas</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>conteudos</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
         <is>
           <t>competencias</t>
         </is>
@@ -553,35 +543,27 @@
       <c r="F2" t="b">
         <v>1</v>
       </c>
-      <c r="G2" t="b">
-        <v>0</v>
+      <c r="G2" t="n">
+        <v>30</v>
       </c>
       <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
         <v>30</v>
       </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>30</v>
-      </c>
-      <c r="M2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>BASICO</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>UA1</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>MATEMATICA</t>
         </is>
@@ -612,45 +594,37 @@
       <c r="F3" t="b">
         <v>1</v>
       </c>
-      <c r="G3" t="b">
-        <v>0</v>
+      <c r="G3" t="n">
+        <v>30</v>
       </c>
       <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
         <v>30</v>
       </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>30</v>
-      </c>
-      <c r="M3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>TECNOLOGICO</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>UA1</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
           <t>COMPUTACAO</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
@@ -681,7 +655,7 @@
       <c r="F4" t="b">
         <v>1</v>
       </c>
-      <c r="G4" t="b">
+      <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
@@ -691,25 +665,17 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K4" t="n">
         <v>15</v>
       </c>
-      <c r="L4" t="n">
-        <v>15</v>
-      </c>
-      <c r="M4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>HUMANISTICO</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>UA1</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>EXTENSAO</t>
         </is>
@@ -737,35 +703,27 @@
       <c r="F5" t="b">
         <v>0</v>
       </c>
-      <c r="G5" t="b">
-        <v>0</v>
+      <c r="G5" t="n">
+        <v>30</v>
       </c>
       <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
         <v>30</v>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>30</v>
-      </c>
-      <c r="M5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>OPTATIVO</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>UA1</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>COMPUTACAO</t>
         </is>

--- a/testes/perfis_exemplo/perfil_minimo/matriz_curricular.xlsx
+++ b/testes/perfis_exemplo/perfil_minimo/matriz_curricular.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Areas" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Temas" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conteudos" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competencias" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -418,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S5"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,42 +480,17 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>nucleo_id</t>
+          <t>observacoes</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>observacoes</t>
+          <t>pre_requisitos</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>pre_requisitos</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
           <t>correquisitos</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>areas</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>temas</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>conteudos</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>competencias</t>
         </is>
       </c>
     </row>
@@ -558,16 +534,6 @@
       <c r="K2" t="n">
         <v>30</v>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>BASICO</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>MATEMATICA</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -609,24 +575,9 @@
       <c r="K3" t="n">
         <v>30</v>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>TECNOLOGICO</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>D1</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>COMPUTACAO</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>C1</t>
         </is>
       </c>
     </row>
@@ -670,16 +621,6 @@
       <c r="K4" t="n">
         <v>15</v>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>HUMANISTICO</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>EXTENSAO</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -717,16 +658,6 @@
       </c>
       <c r="K5" t="n">
         <v>30</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>OPTATIVO</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>COMPUTACAO</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -771,7 +702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -790,6 +721,11 @@
           <t>descricao</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>componentes</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -802,6 +738,11 @@
           <t>Núcleo Básico de Teste</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -814,6 +755,11 @@
           <t>Núcleo Tecnológico de Teste</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -826,6 +772,11 @@
           <t>Núcleo Humanístico de Teste</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EXT1</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -836,6 +787,11 @@
       <c r="B5" t="inlineStr">
         <is>
           <t>Núcleo Optativo de Teste</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>OPT1</t>
         </is>
       </c>
     </row>
@@ -850,7 +806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -869,6 +825,11 @@
           <t>descricao</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>componentes</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -881,6 +842,11 @@
           <t>Matemática</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -893,6 +859,11 @@
           <t>Computação</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>D2|OPT1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -903,6 +874,11 @@
       <c r="B4" t="inlineStr">
         <is>
           <t>Extensão</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EXT1</t>
         </is>
       </c>
     </row>
@@ -917,7 +893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -944,6 +920,11 @@
       <c r="E1" t="inlineStr">
         <is>
           <t>status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>componentes</t>
         </is>
       </c>
     </row>
@@ -958,7 +939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -982,6 +963,73 @@
           <t>fonte</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>componentes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>descricao</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>obrigatoria</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>fonte</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>componentes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Competência de teste</t>
+        </is>
+      </c>
+      <c r="C2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
